--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487923_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487923_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>J. LLAMAS PRADO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1075</v>
+        <v>3.8297</v>
       </c>
       <c r="E2" t="n">
-        <v>6.698</v>
+        <v>5.1511</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.5905</v>
+        <v>-1.3214</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.9212</v>
+        <v>2.4437</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6324</v>
+        <v>1.3603</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.5537</v>
+        <v>1.0834</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6019</v>
+        <v>4.7258</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9839</v>
+        <v>1.7565</v>
       </c>
       <c r="L2" t="n">
-        <v>0.618</v>
+        <v>2.9693</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.5231</v>
+        <v>-2.2821</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.3515</v>
+        <v>-0.3962</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.1717</v>
+        <v>-1.8859</v>
       </c>
       <c r="P2" t="n">
-        <v>1.4568</v>
+        <v>1.2487</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4974</v>
+        <v>1.2487</v>
       </c>
       <c r="S2" t="n">
-        <v>4.448</v>
+        <v>0.3673</v>
       </c>
       <c r="T2" t="n">
-        <v>3.9691</v>
+        <v>0.4253</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4789</v>
+        <v>-0.058</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1238</v>
+        <v>-0.23</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0437</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. LLAMAS PRADO</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0521</v>
+        <v>2.8856</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4615</v>
+        <v>4.8577</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.4095</v>
+        <v>-1.9722</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4437</v>
+        <v>-0.9212</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3603</v>
+        <v>0.6324</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0834</v>
+        <v>-1.5537</v>
       </c>
       <c r="J3" t="n">
-        <v>4.7258</v>
+        <v>2.6019</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7565</v>
+        <v>1.9839</v>
       </c>
       <c r="L3" t="n">
-        <v>2.9693</v>
+        <v>0.618</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.2821</v>
+        <v>-3.5231</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3962</v>
+        <v>-1.3515</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.8859</v>
+        <v>-2.1717</v>
       </c>
       <c r="P3" t="n">
-        <v>1.2487</v>
+        <v>1.4568</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2487</v>
+        <v>2.4974</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4104</v>
+        <v>2.2261</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2643</v>
+        <v>2.1289</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1461</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.23</v>
+        <v>0.1238</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.23</v>
+        <v>-1.0437</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4942</v>
+        <v>2.8749</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1461</v>
+        <v>1.5561</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3481</v>
+        <v>1.3187</v>
       </c>
       <c r="G4" t="n">
         <v>0.7532</v>
@@ -766,13 +766,13 @@
         <v>1.0406</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0072</v>
+        <v>0.3735</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.3415</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0614</v>
+        <v>0.032</v>
       </c>
       <c r="V4" t="n">
         <v>0.7076</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. GONZALEZ CORDERO</t>
+          <t>A. CABRERA GARRANCHO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4643</v>
+        <v>1.4843</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4238</v>
+        <v>3.6706</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0406</v>
+        <v>-2.1863</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2561</v>
+        <v>-0.7177</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3624</v>
+        <v>-0.983</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.1063</v>
+        <v>0.2653</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8399</v>
+        <v>2.8462</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5542</v>
+        <v>-0.1623</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7144</v>
+        <v>3.0085</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5838</v>
+        <v>-3.5639</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1919</v>
+        <v>-0.8207</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3919</v>
+        <v>-2.7432</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6244</v>
+        <v>1.4568</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6244</v>
+        <v>1.4568</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5839</v>
+        <v>0.9751</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5839</v>
+        <v>0.8244</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.1507</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. CABRERA GARRANCHO</t>
+          <t>A. GONZALEZ CORDERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3501</v>
+        <v>1.4643</v>
       </c>
       <c r="E6" t="n">
-        <v>3.7125</v>
+        <v>1.4238</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.3624</v>
+        <v>0.0406</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7177</v>
+        <v>0.2561</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.983</v>
+        <v>1.3624</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2653</v>
+        <v>-1.1063</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8462</v>
+        <v>0.8399</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1623</v>
+        <v>1.5542</v>
       </c>
       <c r="L6" t="n">
-        <v>3.0085</v>
+        <v>-0.7144</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.5639</v>
+        <v>-0.5838</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8207</v>
+        <v>-0.1919</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.7432</v>
+        <v>-0.3919</v>
       </c>
       <c r="P6" t="n">
-        <v>1.4568</v>
+        <v>0.6244</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4568</v>
+        <v>0.6244</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8409</v>
+        <v>0.5839</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8663</v>
+        <v>0.5839</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0254</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2366</v>
+        <v>0.5609</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4241</v>
+        <v>0.135</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6607</v>
+        <v>0.4258</v>
       </c>
       <c r="G7" t="n">
         <v>-1.7067</v>
@@ -1000,13 +1000,13 @@
         <v>2.0812</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6758999999999999</v>
+        <v>1.0001</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1396</v>
+        <v>0.6987</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5363</v>
+        <v>0.3014</v>
       </c>
       <c r="V7" t="n">
         <v>-0.8137</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2459</v>
+        <v>-1.483</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8676</v>
+        <v>-2.0167</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6217</v>
+        <v>0.5337</v>
       </c>
       <c r="G8" t="n">
         <v>-3.1502</v>
@@ -1078,13 +1078,13 @@
         <v>1.4568</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4475</v>
+        <v>0.2104</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1396</v>
+        <v>-0.0095</v>
       </c>
       <c r="U8" t="n">
-        <v>0.308</v>
+        <v>0.2199</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.501</v>
+        <v>-1.9713</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2176</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.7186</v>
+        <v>-2.748</v>
       </c>
       <c r="G9" t="n">
         <v>-3.1676</v>
@@ -1156,13 +1156,13 @@
         <v>0.6244</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4991</v>
+        <v>1.0288</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3353</v>
+        <v>0.8944</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1638</v>
+        <v>0.1344</v>
       </c>
       <c r="V9" t="n">
         <v>0.5838</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8262</v>
+        <v>-2.295</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4596</v>
+        <v>-3.2219</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6333</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="G10" t="n">
         <v>-4.975</v>
@@ -1234,13 +1234,13 @@
         <v>1.4568</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0157</v>
+        <v>0.5155</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0743</v>
+        <v>0.312</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.09</v>
+        <v>0.2036</v>
       </c>
       <c r="V10" t="n">
         <v>0.7076</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9415</v>
+        <v>-4.2188</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8594000000000001</v>
+        <v>-0.3422</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.0821</v>
+        <v>-3.8765</v>
       </c>
       <c r="G11" t="n">
         <v>-1.5842</v>
@@ -1312,13 +1312,13 @@
         <v>1.6649</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0809</v>
+        <v>0.8036</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6582</v>
+        <v>1.1754</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5774</v>
+        <v>-0.3718</v>
       </c>
       <c r="V11" t="n">
         <v>-1.9813</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.3352</v>
+        <v>-5.892</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.5938</v>
+        <v>-3.3562</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.7414</v>
+        <v>-2.5359</v>
       </c>
       <c r="G12" t="n">
         <v>-4.801</v>
@@ -1390,13 +1390,13 @@
         <v>0.8325</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5154</v>
+        <v>-0.0723</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0619</v>
+        <v>0.2996</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5774</v>
+        <v>-0.3718</v>
       </c>
       <c r="V12" t="n">
         <v>0.23</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.2744</v>
+        <v>-9.028</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.0737</v>
+        <v>-3.6217</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.2007</v>
+        <v>-5.4063</v>
       </c>
       <c r="G13" t="n">
         <v>-6.6966</v>
@@ -1468,13 +1468,13 @@
         <v>1.6649</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2141</v>
+        <v>1.4605</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8011</v>
+        <v>1.253</v>
       </c>
       <c r="U13" t="n">
-        <v>0.413</v>
+        <v>0.2075</v>
       </c>
       <c r="V13" t="n">
         <v>-2.3351</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-13.4194</v>
+        <v>-11.7884</v>
       </c>
       <c r="E14" t="n">
-        <v>3.381300000000002</v>
+        <v>5.012300000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>-16.8008</v>
+        <v>-16.8009</v>
       </c>
       <c r="G14" t="n">
         <v>-24.2672</v>
@@ -1531,7 +1531,7 @@
         <v>-27.0256</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.839499999999999</v>
+        <v>-5.8395</v>
       </c>
       <c r="O14" t="n">
         <v>-21.1862</v>
@@ -1546,10 +1546,10 @@
         <v>16.6494</v>
       </c>
       <c r="S14" t="n">
-        <v>7.841600000000001</v>
+        <v>9.4725</v>
       </c>
       <c r="T14" t="n">
-        <v>7.2965</v>
+        <v>8.9276</v>
       </c>
       <c r="U14" t="n">
         <v>0.5450999999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.2905</v>
+        <v>5.9754</v>
       </c>
       <c r="E15" t="n">
-        <v>7.5369</v>
+        <v>7.1083</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2464</v>
+        <v>-1.1329</v>
       </c>
       <c r="G15" t="n">
         <v>7.7512</v>
@@ -1624,13 +1624,13 @@
         <v>1.6649</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8364</v>
+        <v>-1.1515</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6458</v>
+        <v>0.2172</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.4822</v>
+        <v>-1.3687</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.0725</v>
+        <v>5.3655</v>
       </c>
       <c r="E16" t="n">
-        <v>4.0072</v>
+        <v>3.6857</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0653</v>
+        <v>1.6797</v>
       </c>
       <c r="G16" t="n">
         <v>5.2694</v>
@@ -1702,13 +1702,13 @@
         <v>1.4568</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4868</v>
+        <v>-0.2203</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2577</v>
+        <v>-0.0638</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2291</v>
+        <v>-0.1565</v>
       </c>
       <c r="V16" t="n">
         <v>1.9813</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.2672</v>
+        <v>4.1473</v>
       </c>
       <c r="E17" t="n">
-        <v>2.7449</v>
+        <v>2.4235</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5222</v>
+        <v>1.7238</v>
       </c>
       <c r="G17" t="n">
         <v>2.4268</v>
@@ -1780,13 +1780,13 @@
         <v>1.2487</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.349</v>
+        <v>-0.4689</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2577</v>
+        <v>-0.0638</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6067</v>
+        <v>-0.4051</v>
       </c>
       <c r="V17" t="n">
         <v>1.9813</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. CORREIA</t>
+          <t>Z. WILLIAMS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8174</v>
+        <v>1.1909</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7926</v>
+        <v>-0.6815</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0248</v>
+        <v>1.8724</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8215</v>
+        <v>2.4869</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0084</v>
+        <v>1.081</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.187</v>
+        <v>1.4059</v>
       </c>
       <c r="J18" t="n">
-        <v>1.777</v>
+        <v>1.7073</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5026</v>
+        <v>0.3749</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2743</v>
+        <v>1.3324</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9555</v>
+        <v>0.7796</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4942</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4613</v>
+        <v>0.0735</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6244</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2081</v>
+        <v>-2.0812</v>
       </c>
       <c r="R18" t="n">
         <v>0.8325</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6629</v>
+        <v>-0.0473</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6524</v>
+        <v>-0.3076</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3154</v>
+        <v>0.2604</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2914</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.1238</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Z. WILLIAMS</t>
+          <t>L. PAREJO CAMACHO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8044</v>
+        <v>0.7222</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8958</v>
+        <v>1.523</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7002</v>
+        <v>-0.8007</v>
       </c>
       <c r="G19" t="n">
-        <v>2.4869</v>
+        <v>0.7331</v>
       </c>
       <c r="H19" t="n">
-        <v>1.081</v>
+        <v>0.2539</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4059</v>
+        <v>0.4792</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7073</v>
+        <v>1.3088</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3749</v>
+        <v>-0.0236</v>
       </c>
       <c r="L19" t="n">
         <v>1.3324</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7796</v>
+        <v>-0.5757</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7060999999999999</v>
+        <v>0.2775</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0735</v>
+        <v>-0.8532</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.2487</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0812</v>
+        <v>-0.2081</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8325</v>
+        <v>0.2081</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4338</v>
+        <v>-0.8246</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5219</v>
+        <v>-0.3915</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0881</v>
+        <v>-0.4332</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.8137</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.8137</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. PAREJO CAMACHO</t>
+          <t>K. NAVARRO ARRUE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4032</v>
+        <v>0.6456</v>
       </c>
       <c r="E20" t="n">
-        <v>1.523</v>
+        <v>2.2298</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1198</v>
+        <v>-1.5841</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7331</v>
+        <v>1.6805</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2539</v>
+        <v>0.0322</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4792</v>
+        <v>1.6484</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3088</v>
+        <v>2.0807</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0236</v>
+        <v>0.3262</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3324</v>
+        <v>1.7545</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5757</v>
+        <v>-0.4002</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2775</v>
+        <v>-0.294</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8532</v>
+        <v>-0.1061</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2081</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2081</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1437</v>
+        <v>-0.4511</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3915</v>
+        <v>0.1491</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7522</v>
+        <v>-0.6002</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8137</v>
+        <v>-0.5838</v>
       </c>
       <c r="W20" t="n">
-        <v>0.8137</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. NAVARRO ARRUE</t>
+          <t>S. CORREIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4019</v>
+        <v>0.5017</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0154</v>
+        <v>1.3283</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6135</v>
+        <v>-0.8266</v>
       </c>
       <c r="G21" t="n">
-        <v>1.6805</v>
+        <v>0.8215</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0322</v>
+        <v>1.0084</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6484</v>
+        <v>-0.187</v>
       </c>
       <c r="J21" t="n">
-        <v>2.0807</v>
+        <v>1.777</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3262</v>
+        <v>1.5026</v>
       </c>
       <c r="L21" t="n">
-        <v>1.7545</v>
+        <v>0.2743</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4002</v>
+        <v>-0.9555</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.294</v>
+        <v>-0.4942</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1061</v>
+        <v>-0.4613</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.6244</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.2081</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.8325</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6948</v>
+        <v>0.3473</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.1167</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6296</v>
+        <v>0.4639</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5838</v>
+        <v>-1.2914</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.1238</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5838</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1592</v>
+        <v>0.4822</v>
       </c>
       <c r="E22" t="n">
         <v>0.41</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2507</v>
+        <v>0.0722</v>
       </c>
       <c r="G22" t="n">
         <v>-0.376</v>
@@ -2170,13 +2170,13 @@
         <v>0.8325</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5271</v>
+        <v>-0.2042</v>
       </c>
       <c r="T22" t="n">
         <v>0.1272</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6543</v>
+        <v>-0.3314</v>
       </c>
       <c r="V22" t="n">
         <v>0.23</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.969</v>
+        <v>-0.6793</v>
       </c>
       <c r="E23" t="n">
         <v>0.8080000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.777</v>
+        <v>-1.4873</v>
       </c>
       <c r="G23" t="n">
         <v>1.5206</v>
@@ -2248,13 +2248,13 @@
         <v>0.8325</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0327</v>
+        <v>-0.7431</v>
       </c>
       <c r="T23" t="n">
         <v>0.0619</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0947</v>
+        <v>-0.805</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>V. ORLOV STURMAN MAURIN</t>
+          <t>G. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.9407</v>
+        <v>-1.7324</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.6558</v>
+        <v>-1.057</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2849</v>
+        <v>-0.6754</v>
       </c>
       <c r="G24" t="n">
-        <v>2.7121</v>
+        <v>-0.7586000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>1.5462</v>
+        <v>0.4929</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1659</v>
+        <v>-1.2516</v>
       </c>
       <c r="J24" t="n">
-        <v>2.3082</v>
+        <v>-0.048</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8974</v>
+        <v>0.5668</v>
       </c>
       <c r="L24" t="n">
-        <v>1.4108</v>
+        <v>-0.6148</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4039</v>
+        <v>-0.7107</v>
       </c>
       <c r="N24" t="n">
-        <v>0.6488</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2449</v>
+        <v>-0.6368</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.9542</v>
+        <v>1.0406</v>
       </c>
       <c r="Q24" t="n">
-        <v>-5.2029</v>
+        <v>-0.2081</v>
       </c>
       <c r="R24" t="n">
         <v>1.2487</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.5122</v>
+        <v>-1.3067</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2577</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.7699</v>
+        <v>-1.2134</v>
       </c>
       <c r="V24" t="n">
-        <v>0.8137</v>
+        <v>-0.7076</v>
       </c>
       <c r="W24" t="n">
-        <v>1.9813</v>
+        <v>-0.7076</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>G. FERNANDEZ DIAZ</t>
+          <t>V. ORLOV STURMAN MAURIN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.8871</v>
+        <v>-1.7709</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.4856</v>
+        <v>-0.9772999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.4015</v>
+        <v>-0.7936</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.7586000000000001</v>
+        <v>2.7121</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4929</v>
+        <v>1.5462</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.2516</v>
+        <v>1.1659</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.048</v>
+        <v>2.3082</v>
       </c>
       <c r="K25" t="n">
-        <v>0.5668</v>
+        <v>0.8974</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.6148</v>
+        <v>1.4108</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.7107</v>
+        <v>0.4039</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.07389999999999999</v>
+        <v>0.6488</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.6368</v>
+        <v>-0.2449</v>
       </c>
       <c r="P25" t="n">
-        <v>1.0406</v>
+        <v>-3.9542</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.2081</v>
+        <v>-5.2029</v>
       </c>
       <c r="R25" t="n">
         <v>1.2487</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.4615</v>
+        <v>-1.3424</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5219</v>
+        <v>-0.0638</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.9395</v>
+        <v>-1.2786</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.7076</v>
+        <v>0.8137</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.7076</v>
+        <v>1.9813</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>13.4195</v>
+        <v>14.8482</v>
       </c>
       <c r="E26" t="n">
         <v>16.8008</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.3813</v>
+        <v>-1.952500000000001</v>
       </c>
       <c r="G26" t="n">
         <v>24.2675</v>
@@ -2482,19 +2482,19 @@
         <v>10.4059</v>
       </c>
       <c r="S26" t="n">
-        <v>-7.8415</v>
+        <v>-6.412800000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5449000000000001</v>
+        <v>-0.5450999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-7.2965</v>
+        <v>-5.8678</v>
       </c>
       <c r="V26" t="n">
         <v>3.2372</v>
       </c>
       <c r="W26" t="n">
-        <v>6.9698</v>
+        <v>6.969799999999999</v>
       </c>
       <c r="X26" t="n">
         <v>-3.7326</v>
